--- a/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{855CEC5C-468B-4C9D-9D94-66CBE574A853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3273D45C-5385-434E-8CE2-1443F4C9F1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -819,13 +819,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH02,S02aH02,S04aH05,S04aH08,S04aH03,S04aH06,S03aH04,S03aH03,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S01aH03,S02aH06,S03aH05,S03aH08,S04aH07,S03aH02,S01aH06,S02aH03,S01aH02,S04aH04</t>
+    <t>S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S04aH02,S04aH06,S01aH03,S03aH03,S04aH03,S03aH02,S02aH02,S01aH02,S04aH04,S03aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH10,S03aH02,S03aH01,S02aH01,S02aH10,S02aH09,S04aH09,S02aH02,S04aH10,S03aH08,S03aH10,S01aH02,S01aH09,S03aH09,S04aH02,S01aH01,S04aH01,S01aH08,S02aH08,S04aH08</t>
+    <t>S03aH09,S03aH08,S03aH10,S01aH09,S01aH01,S04aH01,S01aH10,S03aH02,S02aH02,S04aH10,S02aH01,S02aH10,S04aH02,S03aH01,S01aH08,S02aH08,S02aH09,S04aH09,S04aH08,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH10,S03aH02,S03aH01,S02aH01,S02aH10,S02aH09,S04aH09,S02aH02,S04aH10,S03aH08,S03aH10,S01aH02,S01aH09,S03aH09,S04aH02,S01aH01,S04aH01,S01aH08,S02aH08,S04aH08</v>
+        <v>S03aH09,S03aH08,S03aH10,S01aH09,S01aH01,S04aH01,S01aH10,S03aH02,S02aH02,S04aH10,S02aH01,S02aH10,S04aH02,S03aH01,S01aH08,S02aH08,S02aH09,S04aH09,S04aH08,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH02,S02aH02,S04aH05,S04aH08,S04aH03,S04aH06,S03aH04,S03aH03,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S01aH03,S02aH06,S03aH05,S03aH08,S04aH07,S03aH02,S01aH06,S02aH03,S01aH02,S04aH04</v>
+        <v>S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S04aH02,S04aH06,S01aH03,S03aH03,S04aH03,S03aH02,S02aH02,S01aH02,S04aH04,S03aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A4D70D1-048C-40B8-B4B5-2AA173279364}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E704AC67-0597-4215-8463-45BA66D24BDE}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1686,7 +1686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA5B5E4-1220-4091-8440-6759EEFAF959}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329DB08E-2E78-4F8F-AE70-DE7DF687BE59}">
   <dimension ref="B9:O1450"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39668,7 +39668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45F272E-0D2E-405F-9844-FC64CE567EBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173427E2-5A81-4C0B-AB51-1EDB6DFC9030}">
   <dimension ref="B9:FT83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -60170,7 +60170,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D84BC0F-C1D7-400F-8389-8249C777664B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C23E8AB-2D88-4725-AA0A-C050D58D78A8}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -60760,7 +60760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC9ADCB0-5D72-4A1E-A023-BF08926B91DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{138A8301-C906-432C-B46F-C7B62282B17B}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61667,7 +61667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EBF937-1054-4AD1-8D88-73BD484AC607}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2AF7C8-8537-4378-BD9D-DE14CC91F14B}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62134,7 +62134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFEF02BD-331D-4AB5-AE7F-F70C116F2153}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACF7199-43F7-4F98-A644-C06A46C9DDF4}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62250,7 +62250,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.24839999999999998</v>
+        <v>0.24840000000000004</v>
       </c>
       <c r="E17" t="s">
         <v>267</v>
@@ -62474,7 +62474,7 @@
         <v>43</v>
       </c>
       <c r="D33">
-        <v>0.26936666666666664</v>
+        <v>0.2693666666666667</v>
       </c>
       <c r="E33" t="s">
         <v>267</v>
@@ -62516,7 +62516,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.27806666666666663</v>
+        <v>0.27806666666666668</v>
       </c>
       <c r="E36" t="s">
         <v>267</v>
@@ -62684,7 +62684,7 @@
         <v>41</v>
       </c>
       <c r="D48">
-        <v>0.33253333333333329</v>
+        <v>0.33253333333333335</v>
       </c>
       <c r="E48" t="s">
         <v>267</v>
@@ -62922,7 +62922,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.24773333333333333</v>
+        <v>0.24773333333333336</v>
       </c>
       <c r="E65" t="s">
         <v>267</v>
@@ -63090,7 +63090,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.31363333333333338</v>
+        <v>0.31363333333333332</v>
       </c>
       <c r="E77" t="s">
         <v>267</v>
@@ -63202,7 +63202,7 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>0.27390000000000003</v>
+        <v>0.27389999999999998</v>
       </c>
       <c r="E85" t="s">
         <v>267</v>
@@ -63300,7 +63300,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.28523333333333328</v>
+        <v>0.28523333333333339</v>
       </c>
       <c r="E92" t="s">
         <v>267</v>
@@ -63412,7 +63412,7 @@
         <v>41</v>
       </c>
       <c r="D100">
-        <v>0.4003666666666667</v>
+        <v>0.40036666666666659</v>
       </c>
       <c r="E100" t="s">
         <v>267</v>
@@ -63468,7 +63468,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.39750000000000002</v>
+        <v>0.39749999999999996</v>
       </c>
       <c r="E104" t="s">
         <v>267</v>
@@ -63482,7 +63482,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.30883333333333329</v>
+        <v>0.30883333333333335</v>
       </c>
       <c r="E105" t="s">
         <v>267</v>
@@ -63650,7 +63650,7 @@
         <v>43</v>
       </c>
       <c r="D117">
-        <v>0.28733333333333338</v>
+        <v>0.28733333333333333</v>
       </c>
       <c r="E117" t="s">
         <v>267</v>
@@ -63748,7 +63748,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.36246666666666671</v>
+        <v>0.36246666666666666</v>
       </c>
       <c r="E124" t="s">
         <v>267</v>
